--- a/docs/downloads/11/tbl_cata_type_alaotra_feramanga_atsimo.xlsx
+++ b/docs/downloads/11/tbl_cata_type_alaotra_feramanga_atsimo.xlsx
@@ -495,12 +495,6 @@
           <t>Cyclone</t>
         </is>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-      <c r="D8">
-        <v>2.2</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -513,12 +507,6 @@
           <t>Grêle</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1.1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -693,12 +681,6 @@
           <t>Incendie / Foudre</t>
         </is>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -711,12 +693,6 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -728,12 +704,6 @@
         <is>
           <t>Criquets</t>
         </is>
-      </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-      <c r="D21">
-        <v>0.4</v>
       </c>
     </row>
   </sheetData>
